--- a/output/pdf_financials_xlsx/ESI.xlsx
+++ b/output/pdf_financials_xlsx/ESI.xlsx
@@ -431,6 +431,19 @@
   </sheetPr>
   <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/ESI.xlsx
+++ b/output/pdf_financials_xlsx/ESI.xlsx
@@ -4108,13 +4108,13 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>332.23</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>292.547</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>237.885</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>315.095</v>
@@ -12642,7 +12642,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ESI.xlsx
+++ b/output/pdf_financials_xlsx/ESI.xlsx
@@ -771,16 +771,16 @@
         <v>2189.864</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>1495.819</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>1033.776</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1147.236</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1299.003</v>
       </c>
       <c r="H10" s="1" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>1621.143</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1586.197</v>
       </c>
     </row>
     <row r="11">
@@ -814,16 +814,16 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1390.978</v>
+        <v>-104.841</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>859.702</v>
+        <v>-174.074</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1000.65</v>
+        <v>-146.586</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1156.357</v>
+        <v>-142.646</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1684.231</v>
+        <v>63.088</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>1638.891</v>
+        <v>52.694</v>
       </c>
     </row>
     <row r="12">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.859</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.367</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.281</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>197.067</v>
+        <v>195.747</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>111.214</v>
+        <v>110.355</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-129.754</v>
+        <v>-129.334</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-204.545</v>
+        <v>-204.178</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-187.796</v>
+        <v>-187.515</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>6.484</v>
@@ -1570,19 +1570,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>445.093</v>
+        <v>443.773</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>410.068</v>
+        <v>409.209</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>205.759</v>
+        <v>206.179</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>145.402</v>
+        <v>145.769</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>138.015</v>
+        <v>138.296</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>421.52</v>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>14.79239786682464</v>
+        <v>14.8225924493414</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>16.91306987770181</v>
+        <v>16.95575908861443</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>13.79253485234597</v>
+        <v>13.82061659921051</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>36.45241045801599</v>
@@ -1767,16 +1767,16 @@
         <v>84.82299999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>28.408</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>20.501</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>28.113</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>16.189</v>
       </c>
     </row>
     <row r="35">
@@ -1849,16 +1849,16 @@
         <v>84.82299999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>28.408</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>20.501</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>28.113</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>16.189</v>
       </c>
     </row>
     <row r="37">
@@ -2341,16 +2341,16 @@
         <v>78.97499999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>96.021</v>
+        <v>67.613</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>77.31</v>
+        <v>56.809</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>78.586</v>
+        <v>50.473</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>60.383</v>
+        <v>44.194</v>
       </c>
     </row>
     <row r="49">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -23098,7 +23098,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -24218,7 +24218,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E287" s="5" t="n">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E288" s="5" t="n">

--- a/output/pdf_financials_xlsx/ESI.xlsx
+++ b/output/pdf_financials_xlsx/ESI.xlsx
@@ -4881,28 +4881,28 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>9.247999999999999</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>14.274</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>6.051</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>6.748</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>39.997</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>15.132</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>31.036</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>10.643</v>
       </c>
     </row>
     <row r="113">
@@ -13892,7 +13892,11 @@
           <t>Proceeds from disposals of property and equipment</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
